--- a/frontend/src/assets/Bank.xlsx
+++ b/frontend/src/assets/Bank.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Jay/Documents/Finance/frontend/src/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Jay/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554D8D6D-8FF1-934C-A3F3-D83D4C0483D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB4B4F0-BD38-0049-9717-06B7CEBBD69D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="620" windowWidth="28040" windowHeight="15920" xr2:uid="{FB563A07-8CD1-EB4D-B38A-60430A0FD5EE}"/>
   </bookViews>
@@ -35,13 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="13">
-  <si>
-    <t>Transaction Type</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
   <si>
     <t>Currency</t>
   </si>
@@ -55,9 +49,6 @@
     <t>Date</t>
   </si>
   <si>
-    <t>transfer</t>
-  </si>
-  <si>
     <t>INR</t>
   </si>
   <si>
@@ -67,13 +58,19 @@
     <t>Business</t>
   </si>
   <si>
-    <t>deposit</t>
-  </si>
-  <si>
     <t>Salary</t>
   </si>
   <si>
     <t>Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit </t>
+  </si>
+  <si>
+    <t>Debit</t>
+  </si>
+  <si>
+    <t>Personal</t>
   </si>
 </sst>
 </file>
@@ -438,53 +435,53 @@
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="17.33203125" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.5" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <v>346827297493</v>
-      </c>
-      <c r="B2" s="1" t="s">
+        <v>123456787658</v>
+      </c>
+      <c r="B2" s="3">
+        <v>10000</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
         <v>6</v>
-      </c>
-      <c r="C2">
-        <v>5000</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
       </c>
       <c r="G2" s="2">
         <v>46011</v>
@@ -492,22 +489,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
-        <v>346827297493</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3">
-        <v>1000</v>
+        <v>123456787658</v>
+      </c>
+      <c r="B3" s="3">
+        <v>20000</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0</v>
       </c>
       <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G3" s="2">
         <v>46012</v>
@@ -515,23 +512,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
-        <v>346827297493</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4">
-        <f>C3+5000</f>
-        <v>6000</v>
+        <v>123456787658</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1">
+        <v>5500</v>
       </c>
       <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
       </c>
       <c r="G4" s="2">
         <v>46013</v>
@@ -539,23 +535,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
-        <v>346827297493</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <f t="shared" ref="C5:C11" si="0">C4+5000</f>
-        <v>11000</v>
+        <v>123456787658</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1">
+        <v>5500</v>
       </c>
       <c r="D5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
         <v>7</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
       </c>
       <c r="G5" s="2">
         <v>46014</v>
@@ -563,32 +558,38 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
-      <c r="B6" s="1"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="1"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="3"/>
-      <c r="B7" s="1"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="1"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="3"/>
-      <c r="B8" s="1"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="1"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
-      <c r="B9" s="1"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="1"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
-      <c r="B10" s="1"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="1"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
-      <c r="B11" s="1"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="1"/>
       <c r="G11" s="2"/>
     </row>
   </sheetData>
